--- a/data_extactor/batch_10_fa/trimmed/batch_0026_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0026_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | تفکر انتقادی | شنیدن فعال | یادگیری فعال | سخن گفتن | راهبردهای یادگیری | نظارت</t>
+          <t>درک مطلب | نگارش | تفکر انتقادی | گوش دادن فعال | یادگیری فعال | سخن گفتن | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>تاریخ و باستان‌شناسی | زبان انگلیسی | جامعه‌شناسی و مردم‌شناسی | جغرافیا | مدیریت و امور اداری | آموزش و تدریس | ارتباطات و رسانه</t>
+          <t>تاریخ و باستان‌شناسی | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | جغرافیا | اداری | آموزش و پرورش | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مردم‌شناسان و باستان‌شناسان | آرشیوداران و بایگان‌های اسناد | موزه‌داران | ویراستاران | استادان تاریخ دانشگاه | تکنسین‌ها و مرمت‌کاران موزه | شاعران، ترانه‌سرایان و نویسندگان خلاق</t>
+          <t>انسان‌شناسان و باستان‌شناسان | کارشناسان اسناد و آرشیو | موزه‌داران | ویراستاران | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌ها و مرمت‌گران موزه | شاعران، ترانه‌سرایان و نویسندگان خلاق</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | یادگیری فعال | تفکر انتقادی | نگارش | راهبردهای یادگیری | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | تفکر انتقادی | نگارش | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>حقوق و امور دولتی | آموزش و تدریس | تاریخ و باستان‌شناسی | ارتباطات و رسانه | جامعه‌شناسی و مردم‌شناسی | جغرافیا</t>
+          <t>قانون و دولت | آموزش و پرورش | تاریخ و باستان‌شناسی | ارتباطات و رسانه | جامعه‌شناسی و انسان‌شناسی | جغرافیا</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | استدلال استقرایی | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | استدلال استقرایی | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تحلیل‌گران سیاست‌گذاری تغییرات اقلیمی | اقتصاددانان | استادان تاریخ دانشگاه | تحلیل‌گران داده‌های اطلاعاتی و امنیتی | قانون‌گذاران و نمایندگان مجلس | استادان علوم سیاسی دانشگاه | جامعه‌شناسان</t>
+          <t>تحلیل‌گران خط‌مشی تغییر اقلیم | اقتصاددانان | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | تحلیل‌گران داده‌ها و اطلاعات امنیتی | نمایندگان مجالس و شوراهای قانون‌گذاری | استادان علوم سیاسی دانشگاه | جامعه‌شناسان</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>جامعه‌شناسی و مردم‌شناسی | ریاضیات | روان‌شناسی | تاریخ و باستان‌شناسی | جغرافیا | حقوق و امور دولتی</t>
+          <t>جامعه‌شناسی و انسان‌شناسی | ریاضیات | روان‌شناسی | تاریخ و باستان‌شناسی | جغرافیا | قانون و دولت</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>جامعه‌شناسان | مردم‌شناسان و باستان‌شناسان | جغرافیدانان | مورخان | دانشمندان و پژوهشگران علوم سیاسی | پژوهشگران نظرسنجی و افکارسنجی | دستیاران پژوهشی علوم اجتماعی</t>
+          <t>جامعه‌شناسان | انسان‌شناسان و باستان‌شناسان | جغرافیدانان | مورخان | دانشمندان و پژوهشگران علوم سیاسی | پژوهشگران پیمایشی و افکارسنجی | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نگارش | شنیدن فعال | درک مطلب | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>حمل و نقل | ریاضیات | جغرافیا | حقوق و امور دولتی | رایانه و الکترونیک | مهندسی و فناوری</t>
+          <t>حمل و نقل | ریاضیات | جغرافیا | قانون و دولت | رایانه و الکترونیک | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی عمران | مهندسان عمران | متخصصان لجستیک و زنجیره تأمین | تحلیل‌گران مدیریت و فرایندها | تکنسین‌های ترافیک | مهندسان حمل‌ونقل | برنامه‌ریزان شهری و منطقه‌ای</t>
+          <t>کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | کارشناسان لجستیک و مدیریت زنجیره تأمین | کارشناسان تحلیل مدیریت و روش‌ها | تکنسین‌های ترافیک | مهندسان حمل‌ونقل و ترافیک | برنامه‌ریزان شهری و منطقه‌ای</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | نگارش | یادگیری فعال | نظارت | سخن گفتن</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | یادگیری فعال | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>تولید و فرآوری مواد غذایی | زیست‌شناسی | شیمی | مکانیک | ریاضیات | مدیریت و امور اداری</t>
+          <t>تولید مواد غذایی | زیست‌شناسی | شیمی | مکانیک | ریاضیات | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | دید نزدیک | درک کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | درک کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | متخصصان علوم دامی | تکنسین‌های علوم زیستی | مدیران مزارع، دامداری‌ها و واحدهای کشاورزی | کارگران زراعت، باغبانی و گلخانه | تکنسین‌های کشاورزی دقیق | متخصصان علوم خاک و گیاه‌شناسی</t>
+          <t>مهندسان کشاورزی | متخصصان علوم دامی | تکنسین‌های علوم زیستی | مدیران امور کشاورزی، دامپروری و شیلات | کارگران زراعت، نهالستان و گلخانه | تکنسین‌های کشاورزی دقیق | متخصصان خاک‌شناسی و علوم گیاهی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | دید نزدیک | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | بینایی نزدیک | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | تکنسین‌های کشاورزی | دانشمندان داده | مدیران مزارع، دامداری‌ها و واحدهای کشاورزی | کاردان‌ها و تکنسین‌های مهندسی صنایع | متخصصان و پژوهشگران سنجش از دور | متخصصان علوم خاک و گیاه‌شناسی</t>
+          <t>مهندسان کشاورزی | تکنسین‌های کشاورزی | دانشمندان داده | مدیران امور کشاورزی، دامپروری و شیلات | کارشناسان و تکنسین‌های مهندسی صنایع | دانشمندان و فناوران سنجش از دور | متخصصان خاک‌شناسی و علوم گیاهی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | سخن گفتن | تفکر انتقادی | مهارت‌های علمی و آزمایشگاهی | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | تفکر انتقادی | علوم | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و فرآوری مواد غذایی | تولید و فراوری صنعتی | شیمی | زبان انگلیسی | رایانه و الکترونیک | زیست‌شناسی | ریاضیات</t>
+          <t>تولید مواد غذایی | تولید و فرآوری | شیمی | زبان انگلیسی | رایانه و الکترونیک | زیست‌شناسی | ریاضیات</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله</t>
+          <t>بینایی نزدیک | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌های کشاورزی | تکنسین‌های شیمی | متصدیان فرمولاسیون و ترکیب مواد غذایی | متخصصان و دانشمندان صنایع غذایی | درجه‌بندی‌کنندگان و سورت‌کنندگان محصولات کشاورزی | بازرسان، نمونه‌برداران و آزمون‌گران کنترل کیفیت کالا | تحلیل‌گران کنترل کیفیت فرایند</t>
+          <t>تکنسین‌های کشاورزی | تکنسین‌های شیمی | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | متخصصان و کارشناسان علوم و صنایع غذایی | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | کارشناسان تحلیل کنترل کیفیت</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | مهارت‌های علمی و آزمایشگاهی | شنیدن فعال | یادگیری فعال | نگارش | سخن گفتن | نظارت | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | علوم | گوش دادن فعال | یادگیری فعال | نگارش | سخن گفتن | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | استدلال استقرایی | بیان شفاهی | مرتب‌سازی اطلاعات | استدلال قیاسی | درک کتبی</t>
+          <t>بینایی نزدیک | درک شفاهی | استدلال استقرایی | بیان شفاهی | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک کتبی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌های کشاورزی | زیست‌شناسان | تکنسین‌های شیمی | تکنسین‌های سیتوژنتیک | تکنسین‌های بافت‌شناسی و آزمایشگاه پاتولوژی | تکنسین‌های آزمایشگاه تشخیص طبی و بالینی | میکروبیولوژیست‌ها</t>
+          <t>تکنسین‌های کشاورزی | زیست‌شناسان | تکنسین‌های شیمی | کارشناسان سیتوژنتیک | کاردان‌های پاتولوژی و بافت‌شناسی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | میکروبیولوژیست‌ها</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>مهارت‌های علمی و آزمایشگاهی | تفکر انتقادی | درک مطلب | شنیدن فعال | نگارش | نظارت | سخن گفتن | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
+          <t>علوم | تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | نظارت | سخن گفتن | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک کتبی | بیان کتبی | درک شفاهی | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>بینایی نزدیک | درک کتبی | بیان کتبی | درک شفاهی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان شیمی | اپراتورها و متصدیان تجهیزات شیمیایی | شیمی‌دانان | تکنسین‌های صنایع غذایی | بازرسان، نمونه‌برداران و آزمون‌گران کنترل کیفیت کالا | تکنسین‌های آزمایشگاه تشخیص طبی و بالینی | تحلیل‌گران کنترل کیفیت فرایند</t>
+          <t>مهندسان شیمی | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | شیمی‌دانان | تکنسین‌های علوم و صنایع غذایی | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان تحلیل کنترل کیفیت</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | سخن گفتن | تفکر انتقادی | نظارت | مهارت‌های علمی و آزمایشگاهی | ریاضیات | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | تفکر انتقادی | نظارت | علوم | ریاضیات | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>شیمی | زیست‌شناسی | حقوق و امور دولتی | ریاضیات | ایمنی و امنیت عمومی | مهندسی و فناوری</t>
+          <t>شیمی | زیست‌شناسی | قانون و دولت | ریاضیات | ایمنی و امنیت عمومی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | دید نزدیک | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌های شیمی | بازرسان انطباق و نظارت زیست‌محیطی | کاردان‌ها و تکنسین‌های مهندسی محیط زیست | مهندسان محیط زیست | کارشناسان و متخصصان علوم محیط زیست و بهداشت محیط | تکنسین‌های هیدرولوژی و آب‌شناسی | اپراتورها و متصدیان تصفیه‌خانه‌های آب و فاضلاب صنعتی و شهری</t>
+          <t>تکنسین‌های شیمی | بازرسان رعایت ضوابط زیست‌محیطی | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط‌زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | تکنسین‌های آب‌شناسی و هیدرولوژی | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
